--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/01_CMP1 - Müşteri Şartları ve Belgelendirme/EKG-YNT-MTR-01_stellantis_csr_uyum_matrisi_gereklilik__ekol_belgesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/01_CMP1 - Müşteri Şartları ve Belgelendirme/EKG-YNT-MTR-01_stellantis_csr_uyum_matrisi_gereklilik__ekol_belgesi.xlsx
@@ -870,7 +870,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Stellantis CSR Uyum Matrisi (gereklilik ↔ Ekol belgesi)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Kaynaksız %85 hedefi kaldırıldı; güncel resmî kaynak ve saha kanıtı şartı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f0e40173da34af9"/>
   <x:tableParts count="1">
@@ -1355,7 +1356,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Stellantis CSR Uyum Matrisi (gereklilik ↔ Ekol belgesi)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Kaynaksız %85 hedefi kaldırıldı; güncel resmî kaynak ve saha kanıtı şartı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R415df516ce4246b4"/>
   <x:tableParts count="1">
@@ -1654,7 +1656,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Stellantis CSR Uyum Matrisi (gereklilik ↔ Ekol belgesi)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Kaynaksız %85 hedefi kaldırıldı; güncel resmî kaynak ve saha kanıtı şartı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a125ac315e34d98"/>
   <x:tableParts count="1">
